--- a/exports/trend_1d/DRREDDY_full_report.xlsx
+++ b/exports/trend_1d/DRREDDY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:U86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>6.08</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>646.65</v>
+        <v>627.8</v>
       </c>
       <c r="I2" t="n">
         <v>636.0694911625001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.22</v>
+        <v>-3.13</v>
       </c>
       <c r="L2" t="n">
-        <v>2.11</v>
+        <v>3.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0.87</v>
+        <v>1.65</v>
       </c>
       <c r="N2" t="n">
         <v>4.09</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="H3" t="n">
-        <v>630.5</v>
+        <v>666.25</v>
       </c>
       <c r="I3" t="n">
         <v>661.1128800195013</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.43</v>
+        <v>-6.12</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>6.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.57</v>
+        <v>1.35</v>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>5.67</v>
       </c>
       <c r="O3" t="n">
         <v>-2.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>713.4</v>
+        <v>692.4</v>
       </c>
       <c r="I4" t="n">
         <v>699.0024548406991</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K4" t="n">
-        <v>7.08</v>
+        <v>3.92</v>
       </c>
       <c r="L4" t="n">
         <v>4.17</v>
@@ -669,7 +716,7 @@
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="O4" t="n">
         <v>5.67</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.09</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H5" t="n">
-        <v>699.3</v>
+        <v>724.5</v>
       </c>
       <c r="I5" t="n">
         <v>722.340611248646</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>-1</v>
+        <v>-4.64</v>
       </c>
       <c r="L5" t="n">
-        <v>4.39</v>
+        <v>4.97</v>
       </c>
       <c r="M5" t="n">
         <v>2.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>-2.94</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.75</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42163</v>
+        <v>42164</v>
       </c>
       <c r="H6" t="n">
-        <v>681.4</v>
+        <v>664.4</v>
       </c>
       <c r="I6" t="n">
         <v>670.5548916768309</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.95</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>6.31</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>1.47</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="O6" t="n">
         <v>3.6</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.27</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42180</v>
+        <v>42181</v>
       </c>
       <c r="H7" t="n">
-        <v>697.1</v>
+        <v>706</v>
       </c>
       <c r="I7" t="n">
         <v>703.1408565044683</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.92</v>
+        <v>-6.26</v>
       </c>
       <c r="L7" t="n">
-        <v>5.64</v>
+        <v>6.56</v>
       </c>
       <c r="M7" t="n">
         <v>0.82</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42251</v>
+        <v>42254</v>
       </c>
       <c r="H8" t="n">
-        <v>810.55</v>
+        <v>789.3</v>
       </c>
       <c r="I8" t="n">
         <v>802.3066825562283</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K8" t="n">
-        <v>14.81</v>
+        <v>11.8</v>
       </c>
       <c r="L8" t="n">
         <v>2.89</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.21</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42271</v>
+        <v>42275</v>
       </c>
       <c r="H9" t="n">
-        <v>794.05</v>
+        <v>838.25</v>
       </c>
       <c r="I9" t="n">
         <v>837.4811225333195</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6</v>
+        <v>-6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>3.76</v>
+        <v>7.11</v>
       </c>
       <c r="M9" t="n">
         <v>2.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>5.57</v>
       </c>
       <c r="O9" t="n">
         <v>-2.62</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42313</v>
+        <v>42314</v>
       </c>
       <c r="H10" t="n">
-        <v>849.9</v>
+        <v>726.15</v>
       </c>
       <c r="I10" t="n">
         <v>810.1935392503066</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10" t="n">
-        <v>1.39</v>
+        <v>-13.37</v>
       </c>
       <c r="L10" t="n">
-        <v>5.28</v>
+        <v>13.75</v>
       </c>
       <c r="M10" t="n">
         <v>1.27</v>
       </c>
       <c r="N10" t="n">
-        <v>3.39</v>
+        <v>14.56</v>
       </c>
       <c r="O10" t="n">
         <v>5.57</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>21.71</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H11" t="n">
-        <v>602.25</v>
+        <v>621.1</v>
       </c>
       <c r="I11" t="n">
         <v>611.2985342022686</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" t="n">
-        <v>17.06</v>
+        <v>14.47</v>
       </c>
       <c r="L11" t="n">
         <v>18.21</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42457</v>
+        <v>42458</v>
       </c>
       <c r="H12" t="n">
-        <v>607.15</v>
+        <v>588.25</v>
       </c>
       <c r="I12" t="n">
         <v>593.8981437850081</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.25</v>
+        <v>-5.29</v>
       </c>
       <c r="L12" t="n">
         <v>9.42</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.82</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42507</v>
+        <v>42508</v>
       </c>
       <c r="H13" t="n">
-        <v>603.55</v>
+        <v>605.05</v>
       </c>
       <c r="I13" t="n">
         <v>604.170758427278</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.6</v>
+        <v>-2.86</v>
       </c>
       <c r="L13" t="n">
         <v>7.74</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42537</v>
+        <v>42538</v>
       </c>
       <c r="H14" t="n">
-        <v>609.65</v>
+        <v>600.6</v>
       </c>
       <c r="I14" t="n">
         <v>606.2862140494558</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>0.76</v>
+        <v>-0.74</v>
       </c>
       <c r="L14" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M14" t="n">
         <v>1.25</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="H15" t="n">
-        <v>630.65</v>
+        <v>649.3</v>
       </c>
       <c r="I15" t="n">
         <v>638.240624985208</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-5</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>5.86</v>
+        <v>8.82</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
         <v>-1.48</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.72</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42576</v>
+        <v>42577</v>
       </c>
       <c r="H16" t="n">
-        <v>696.45</v>
+        <v>663.95</v>
       </c>
       <c r="I16" t="n">
         <v>684.2969310048927</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>7.26</v>
+        <v>2.26</v>
       </c>
       <c r="L16" t="n">
         <v>3.53</v>
@@ -1353,7 +1544,7 @@
         <v>0.83</v>
       </c>
       <c r="N16" t="n">
-        <v>3.26</v>
+        <v>4.67</v>
       </c>
       <c r="O16" t="n">
         <v>2.96</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H17" t="n">
-        <v>627.75</v>
+        <v>637.7</v>
       </c>
       <c r="I17" t="n">
         <v>633.4268603398235</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>5.45</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>5.97</v>
@@ -1410,7 +1613,7 @@
         <v>0.84</v>
       </c>
       <c r="N17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
         <v>-4.67</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.13</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42649</v>
+        <v>42650</v>
       </c>
       <c r="H18" t="n">
-        <v>615.45</v>
+        <v>610.85</v>
       </c>
       <c r="I18" t="n">
         <v>614.623498175809</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.49</v>
+        <v>-4.21</v>
       </c>
       <c r="L18" t="n">
-        <v>4.08</v>
+        <v>4.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.26</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.41</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42667</v>
+        <v>42668</v>
       </c>
       <c r="H19" t="n">
-        <v>617.85</v>
+        <v>640.1</v>
       </c>
       <c r="I19" t="n">
         <v>637.1545546107665</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.15</v>
+        <v>-4.79</v>
       </c>
       <c r="L19" t="n">
-        <v>2.91</v>
+        <v>5.07</v>
       </c>
       <c r="M19" t="n">
         <v>0.66</v>
       </c>
       <c r="N19" t="n">
-        <v>1.13</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>-0.75</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>7.39</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H20" t="n">
-        <v>652.45</v>
+        <v>615.95</v>
       </c>
       <c r="I20" t="n">
         <v>631.3503811404107</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>1.93</v>
+        <v>-3.77</v>
       </c>
       <c r="L20" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>2.89</v>
       </c>
       <c r="N20" t="n">
-        <v>1.98</v>
+        <v>5.59</v>
       </c>
       <c r="O20" t="n">
         <v>3.6</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42767</v>
+        <v>42768</v>
       </c>
       <c r="H21" t="n">
-        <v>600.25</v>
+        <v>619.4</v>
       </c>
       <c r="I21" t="n">
         <v>616.6757166372116</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="n">
-        <v>2.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>8.94</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H22" t="n">
-        <v>588.3</v>
+        <v>582.25</v>
       </c>
       <c r="I22" t="n">
         <v>584.984026049429</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.02</v>
+        <v>-6</v>
       </c>
       <c r="L22" t="n">
-        <v>5.23</v>
+        <v>6.16</v>
       </c>
       <c r="M22" t="n">
         <v>0.06</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H23" t="n">
-        <v>535.15</v>
+        <v>544.8</v>
       </c>
       <c r="I23" t="n">
         <v>540.1726292761539</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K23" t="n">
-        <v>8.09</v>
+        <v>6.43</v>
       </c>
       <c r="L23" t="n">
         <v>1.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H24" t="n">
-        <v>515.9</v>
+        <v>503.35</v>
       </c>
       <c r="I24" t="n">
         <v>512.0490032576838</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.3</v>
+        <v>-7.61</v>
       </c>
       <c r="L24" t="n">
-        <v>6.65</v>
+        <v>7.86</v>
       </c>
       <c r="M24" t="n">
         <v>1.53</v>
       </c>
       <c r="N24" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="O24" t="n">
         <v>1.8</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>42899</v>
+        <v>42900</v>
       </c>
       <c r="H25" t="n">
-        <v>525.35</v>
+        <v>533.85</v>
       </c>
       <c r="I25" t="n">
         <v>527.7261062473839</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.37</v>
+        <v>-6.06</v>
       </c>
       <c r="L25" t="n">
-        <v>5.94</v>
+        <v>7.24</v>
       </c>
       <c r="M25" t="n">
         <v>2.98</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.98</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>42943</v>
+        <v>42944</v>
       </c>
       <c r="H26" t="n">
-        <v>524.05</v>
+        <v>493</v>
       </c>
       <c r="I26" t="n">
         <v>523.1954971901274</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.84</v>
+        <v>-7.65</v>
       </c>
       <c r="L26" t="n">
-        <v>3.08</v>
+        <v>8.18</v>
       </c>
       <c r="M26" t="n">
-        <v>0.83</v>
+        <v>4.61</v>
       </c>
       <c r="N26" t="n">
-        <v>3.21</v>
+        <v>5.93</v>
       </c>
       <c r="O26" t="n">
         <v>1.62</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H27" t="n">
-        <v>404.2</v>
+        <v>443.5</v>
       </c>
       <c r="I27" t="n">
         <v>438.1579053697083</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>18.01</v>
+        <v>10.04</v>
       </c>
       <c r="L27" t="n">
         <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0.73</v>
+        <v>4.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.43</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-5.93</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.98</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43069</v>
+        <v>43070</v>
       </c>
       <c r="H28" t="n">
-        <v>456.8</v>
+        <v>446.8</v>
       </c>
       <c r="I28" t="n">
         <v>450.4006213130139</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0.74</v>
       </c>
       <c r="L28" t="n">
         <v>6.82</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H29" t="n">
-        <v>462.15</v>
+        <v>474.3</v>
       </c>
       <c r="I29" t="n">
         <v>467.5017210514027</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.44</v>
+        <v>-6.15</v>
       </c>
       <c r="L29" t="n">
-        <v>4.14</v>
+        <v>6.54</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H30" t="n">
-        <v>501.55</v>
+        <v>471.4</v>
       </c>
       <c r="I30" t="n">
         <v>478.1359395433093</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K30" t="n">
-        <v>5.75</v>
+        <v>-0.61</v>
       </c>
       <c r="L30" t="n">
         <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="N30" t="n">
-        <v>2.92</v>
+        <v>6.01</v>
       </c>
       <c r="O30" t="n">
         <v>2.63</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.58</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H31" t="n">
-        <v>416.65</v>
+        <v>438.15</v>
       </c>
       <c r="I31" t="n">
         <v>417.229413007405</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K31" t="n">
-        <v>11.61</v>
+        <v>7.05</v>
       </c>
       <c r="L31" t="n">
         <v>4.03</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.28</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H32" t="n">
-        <v>463.95</v>
+        <v>418.8</v>
       </c>
       <c r="I32" t="n">
         <v>437.0486420822839</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>5.89</v>
+        <v>-4.42</v>
       </c>
       <c r="L32" t="n">
-        <v>4.28</v>
+        <v>5.51</v>
       </c>
       <c r="M32" t="n">
-        <v>1.34</v>
+        <v>4.17</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>9.73</v>
       </c>
       <c r="O32" t="n">
         <v>5.16</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.32</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43314</v>
+        <v>43315</v>
       </c>
       <c r="H33" t="n">
-        <v>445.55</v>
+        <v>456.2</v>
       </c>
       <c r="I33" t="n">
         <v>452.5032654407958</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.39</v>
+        <v>-8.93</v>
       </c>
       <c r="L33" t="n">
-        <v>6.88</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H34" t="n">
-        <v>497.9</v>
+        <v>474.5</v>
       </c>
       <c r="I34" t="n">
         <v>475.8656766823929</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K34" t="n">
-        <v>9.140000000000001</v>
+        <v>4.01</v>
       </c>
       <c r="L34" t="n">
         <v>3.33</v>
       </c>
       <c r="M34" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="O34" t="n">
         <v>2.39</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43432</v>
+        <v>43433</v>
       </c>
       <c r="H35" t="n">
-        <v>514.45</v>
+        <v>531.05</v>
       </c>
       <c r="I35" t="n">
         <v>526.7745843274137</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.42</v>
+        <v>-11.92</v>
       </c>
       <c r="L35" t="n">
-        <v>11.91</v>
+        <v>12.4</v>
       </c>
       <c r="M35" t="n">
         <v>6.74</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>10.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H36" t="n">
-        <v>533.45</v>
+        <v>512.65</v>
       </c>
       <c r="I36" t="n">
         <v>520.7117292214406</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" t="n">
-        <v>0.45</v>
+        <v>-3.46</v>
       </c>
       <c r="L36" t="n">
-        <v>4.57</v>
+        <v>29.46</v>
       </c>
       <c r="M36" t="n">
         <v>3.96</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.04</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43543</v>
+        <v>43544</v>
       </c>
       <c r="H37" t="n">
-        <v>541.75</v>
+        <v>550.35</v>
       </c>
       <c r="I37" t="n">
         <v>543.6325455108284</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.68</v>
+        <v>-7.35</v>
       </c>
       <c r="L37" t="n">
-        <v>6.35</v>
+        <v>7.68</v>
       </c>
       <c r="M37" t="n">
         <v>3.38</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43601</v>
+        <v>43602</v>
       </c>
       <c r="H38" t="n">
-        <v>560.2</v>
+        <v>549</v>
       </c>
       <c r="I38" t="n">
         <v>556.4613952649705</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K38" t="n">
-        <v>1.79</v>
+        <v>-0.25</v>
       </c>
       <c r="L38" t="n">
-        <v>1.59</v>
+        <v>3.06</v>
       </c>
       <c r="M38" t="n">
         <v>0.92</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H39" t="n">
-        <v>520.55</v>
+        <v>536.5</v>
       </c>
       <c r="I39" t="n">
         <v>534.046267586989</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K39" t="n">
-        <v>5.18</v>
+        <v>2.28</v>
       </c>
       <c r="L39" t="n">
         <v>2.37</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.78</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43885</v>
+        <v>43886</v>
       </c>
       <c r="H40" t="n">
-        <v>635.25</v>
+        <v>617.4</v>
       </c>
       <c r="I40" t="n">
         <v>619.3618923708354</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K40" t="n">
-        <v>18.41</v>
+        <v>15.08</v>
       </c>
       <c r="L40" t="n">
         <v>3.96</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43920</v>
+        <v>43921</v>
       </c>
       <c r="H41" t="n">
-        <v>598.85</v>
+        <v>624.15</v>
       </c>
       <c r="I41" t="n">
         <v>617.2258085645647</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>-1.09</v>
       </c>
       <c r="L41" t="n">
         <v>4.7</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>19.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H42" t="n">
-        <v>874.85</v>
+        <v>852.95</v>
       </c>
       <c r="I42" t="n">
         <v>856.3298524228333</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K42" t="n">
-        <v>40.17</v>
+        <v>36.66</v>
       </c>
       <c r="L42" t="n">
         <v>3.07</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44089</v>
+        <v>44090</v>
       </c>
       <c r="H43" t="n">
-        <v>888.45</v>
+        <v>925.6</v>
       </c>
       <c r="I43" t="n">
         <v>924.9733348813724</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.16</v>
+        <v>-8.52</v>
       </c>
       <c r="L43" t="n">
-        <v>6.67</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>4.18</v>
       </c>
       <c r="O43" t="n">
         <v>-2.5</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.64</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H44" t="n">
-        <v>975.95</v>
+        <v>939.6</v>
       </c>
       <c r="I44" t="n">
         <v>954.0149393744656</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>5.44</v>
+        <v>1.51</v>
       </c>
       <c r="L44" t="n">
         <v>4.69</v>
       </c>
       <c r="M44" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="N44" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="O44" t="n">
         <v>4.18</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44181</v>
+        <v>44182</v>
       </c>
       <c r="H45" t="n">
-        <v>1007.8</v>
+        <v>1014.55</v>
       </c>
       <c r="I45" t="n">
         <v>1013.529709320805</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.26</v>
+        <v>-7.98</v>
       </c>
       <c r="L45" t="n">
-        <v>8.56</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>1.68</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.92</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H46" t="n">
-        <v>1042.55</v>
+        <v>1010.4</v>
       </c>
       <c r="I46" t="n">
         <v>1016.799123983666</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>2.76</v>
+        <v>-0.41</v>
       </c>
       <c r="L46" t="n">
         <v>2.69</v>
@@ -3063,7 +3614,7 @@
         <v>0.61</v>
       </c>
       <c r="N46" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
         <v>0.67</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.34</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H47" t="n">
-        <v>923.85</v>
+        <v>938.55</v>
       </c>
       <c r="I47" t="n">
         <v>923.8818102976167</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K47" t="n">
-        <v>8.57</v>
+        <v>7.11</v>
       </c>
       <c r="L47" t="n">
         <v>3.68</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.31</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H48" t="n">
-        <v>1082.25</v>
+        <v>968.65</v>
       </c>
       <c r="I48" t="n">
         <v>1058.707483161714</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K48" t="n">
-        <v>15.31</v>
+        <v>3.21</v>
       </c>
       <c r="L48" t="n">
         <v>1.1</v>
@@ -3177,7 +3752,7 @@
         <v>0.4</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="O48" t="n">
         <v>1.59</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>14.21</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H49" t="n">
-        <v>952.7</v>
+        <v>971.95</v>
       </c>
       <c r="I49" t="n">
         <v>963.6679346020393</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K49" t="n">
-        <v>1.65</v>
+        <v>-0.34</v>
       </c>
       <c r="L49" t="n">
         <v>12.42</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>2.15</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>6.42</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H50" t="n">
-        <v>950.8</v>
+        <v>930.35</v>
       </c>
       <c r="I50" t="n">
         <v>944.196773954288</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.18</v>
+        <v>-4.28</v>
       </c>
       <c r="L50" t="n">
-        <v>2.92</v>
+        <v>5.34</v>
       </c>
       <c r="M50" t="n">
         <v>0.57</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44558</v>
+        <v>44559</v>
       </c>
       <c r="H51" t="n">
-        <v>948.75</v>
+        <v>966.65</v>
       </c>
       <c r="I51" t="n">
         <v>963.4005195472706</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.98</v>
+        <v>-3.9</v>
       </c>
       <c r="L51" t="n">
         <v>5.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.67</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H52" t="n">
-        <v>937</v>
+        <v>918.3</v>
       </c>
       <c r="I52" t="n">
         <v>925.6911698266423</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.07</v>
+        <v>-5</v>
       </c>
       <c r="L52" t="n">
-        <v>4.71</v>
+        <v>5.45</v>
       </c>
       <c r="M52" t="n">
         <v>0.51</v>
       </c>
       <c r="N52" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>1.89</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.12</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H53" t="n">
-        <v>825.45</v>
+        <v>865.7</v>
       </c>
       <c r="I53" t="n">
         <v>830.5878738372394</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K53" t="n">
-        <v>10.11</v>
+        <v>5.73</v>
       </c>
       <c r="L53" t="n">
         <v>2.62</v>
@@ -3462,7 +4097,7 @@
         <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>2.96</v>
+        <v>4.88</v>
       </c>
       <c r="O53" t="n">
         <v>-2</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.54</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H54" t="n">
-        <v>830.9</v>
+        <v>815.4</v>
       </c>
       <c r="I54" t="n">
         <v>818.1275962586468</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.02</v>
+        <v>-5.81</v>
       </c>
       <c r="L54" t="n">
         <v>6.18</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44700</v>
+        <v>44701</v>
       </c>
       <c r="H55" t="n">
-        <v>785.9</v>
+        <v>849.8</v>
       </c>
       <c r="I55" t="n">
         <v>827.4733164770156</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>3.62</v>
+        <v>-4.22</v>
       </c>
       <c r="L55" t="n">
-        <v>4.64</v>
+        <v>5.45</v>
       </c>
       <c r="M55" t="n">
         <v>1.45</v>
       </c>
       <c r="N55" t="n">
-        <v>1.14</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O55" t="n">
         <v>-1.87</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.92</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44767</v>
+        <v>44768</v>
       </c>
       <c r="H56" t="n">
-        <v>866.1</v>
+        <v>842.4</v>
       </c>
       <c r="I56" t="n">
         <v>848.8678520267252</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K56" t="n">
-        <v>1.92</v>
+        <v>-0.87</v>
       </c>
       <c r="L56" t="n">
         <v>6.45</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H57" t="n">
-        <v>853.95</v>
+        <v>872.15</v>
       </c>
       <c r="I57" t="n">
         <v>859.0607567550301</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.37</v>
+        <v>-3.53</v>
       </c>
       <c r="L57" t="n">
-        <v>2.8</v>
+        <v>4.63</v>
       </c>
       <c r="M57" t="n">
         <v>1.21</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.95</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44918</v>
+        <v>44921</v>
       </c>
       <c r="H58" t="n">
-        <v>862.1</v>
+        <v>849.7</v>
       </c>
       <c r="I58" t="n">
         <v>855.3134248516591</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.15</v>
+        <v>-2.57</v>
       </c>
       <c r="L58" t="n">
         <v>3.34</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.88</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H59" t="n">
-        <v>888.05</v>
+        <v>897.55</v>
       </c>
       <c r="I59" t="n">
         <v>889.7826041833273</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.51</v>
+        <v>-5.63</v>
       </c>
       <c r="L59" t="n">
-        <v>5.17</v>
+        <v>5.84</v>
       </c>
       <c r="M59" t="n">
         <v>1.88</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H60" t="n">
-        <v>973.45</v>
+        <v>906.4</v>
       </c>
       <c r="I60" t="n">
         <v>947.7776136235229</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K60" t="n">
-        <v>8.460000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="L60" t="n">
         <v>4.25</v>
       </c>
       <c r="M60" t="n">
-        <v>0.97</v>
+        <v>3.95</v>
       </c>
       <c r="N60" t="n">
-        <v>2.36</v>
+        <v>6.89</v>
       </c>
       <c r="O60" t="n">
         <v>1.07</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="H61" t="n">
-        <v>935.15</v>
+        <v>940.4</v>
       </c>
       <c r="I61" t="n">
         <v>938.2248513994946</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.17</v>
+        <v>-3.75</v>
       </c>
       <c r="L61" t="n">
-        <v>3.82</v>
+        <v>4.34</v>
       </c>
       <c r="M61" t="n">
         <v>0.68</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.06</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H62" t="n">
-        <v>1144.75</v>
+        <v>1129.95</v>
       </c>
       <c r="I62" t="n">
         <v>1131.890997492056</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K62" t="n">
-        <v>21.73</v>
+        <v>20.16</v>
       </c>
       <c r="L62" t="n">
         <v>0.9399999999999999</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.09</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="H63" t="n">
-        <v>1129.3</v>
+        <v>1132.9</v>
       </c>
       <c r="I63" t="n">
         <v>1130.357617037558</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K63" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="L63" t="n">
         <v>3.42</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.45</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45268</v>
+        <v>45271</v>
       </c>
       <c r="H64" t="n">
-        <v>1152.8</v>
+        <v>1094.7</v>
       </c>
       <c r="I64" t="n">
         <v>1102.590072111431</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K64" t="n">
-        <v>1.76</v>
+        <v>-3.37</v>
       </c>
       <c r="L64" t="n">
-        <v>0.98</v>
+        <v>5.2</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="N64" t="n">
-        <v>0.8</v>
+        <v>5.04</v>
       </c>
       <c r="O64" t="n">
         <v>0.32</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.78</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45287</v>
+        <v>45288</v>
       </c>
       <c r="H65" t="n">
-        <v>1142.9</v>
+        <v>1171.7</v>
       </c>
       <c r="I65" t="n">
         <v>1168.962527187029</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.4</v>
+        <v>-7.03</v>
       </c>
       <c r="L65" t="n">
-        <v>4.54</v>
+        <v>7.62</v>
       </c>
       <c r="M65" t="n">
         <v>0.52</v>
       </c>
       <c r="N65" t="n">
-        <v>1.46</v>
+        <v>2.52</v>
       </c>
       <c r="O65" t="n">
         <v>-5.04</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="H66" t="n">
-        <v>1226.95</v>
+        <v>1208.8</v>
       </c>
       <c r="I66" t="n">
         <v>1216.989552978059</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K66" t="n">
-        <v>4.72</v>
+        <v>3.17</v>
       </c>
       <c r="L66" t="n">
         <v>5.77</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.92</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H67" t="n">
-        <v>1250.4</v>
+        <v>1259.4</v>
       </c>
       <c r="I67" t="n">
         <v>1258.95838842256</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.44</v>
+        <v>-4.19</v>
       </c>
       <c r="L67" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="M67" t="n">
         <v>0.93</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.96</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H68" t="n">
-        <v>1211.25</v>
+        <v>1175.45</v>
       </c>
       <c r="I68" t="n">
         <v>1187.191749383605</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.82</v>
+        <v>-6.67</v>
       </c>
       <c r="L68" t="n">
-        <v>5.47</v>
+        <v>6.78</v>
       </c>
       <c r="M68" t="n">
         <v>2.52</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45469</v>
+        <v>45470</v>
       </c>
       <c r="H69" t="n">
-        <v>1214</v>
+        <v>1247.2</v>
       </c>
       <c r="I69" t="n">
         <v>1224.72759991178</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.28</v>
+        <v>-6.1</v>
       </c>
       <c r="L69" t="n">
-        <v>4.77</v>
+        <v>6.33</v>
       </c>
       <c r="M69" t="n">
         <v>2.53</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.78</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="H70" t="n">
-        <v>1333.45</v>
+        <v>1331.2</v>
       </c>
       <c r="I70" t="n">
         <v>1331.261935878596</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K70" t="n">
-        <v>6.92</v>
+        <v>6.74</v>
       </c>
       <c r="L70" t="n">
         <v>3.86</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.35</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H71" t="n">
-        <v>1275.4</v>
+        <v>1325.6</v>
       </c>
       <c r="I71" t="n">
         <v>1296.502095239835</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K71" t="n">
-        <v>4.19</v>
+        <v>0.42</v>
       </c>
       <c r="L71" t="n">
         <v>2.09</v>
@@ -4488,7 +5339,7 @@
         <v>1.61</v>
       </c>
       <c r="N71" t="n">
-        <v>2.35</v>
+        <v>3.94</v>
       </c>
       <c r="O71" t="n">
         <v>-0.17</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.6</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="H72" t="n">
-        <v>1302.35</v>
+        <v>1288.15</v>
       </c>
       <c r="I72" t="n">
         <v>1288.166889386094</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.75</v>
+        <v>-2.83</v>
       </c>
       <c r="L72" t="n">
         <v>4.07</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.87</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H73" t="n">
-        <v>1172.1</v>
+        <v>1187.2</v>
       </c>
       <c r="I73" t="n">
         <v>1173.479628182987</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K73" t="n">
-        <v>9.01</v>
+        <v>7.84</v>
       </c>
       <c r="L73" t="n">
         <v>1.93</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.16</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H74" t="n">
-        <v>1151.45</v>
+        <v>1109.95</v>
       </c>
       <c r="I74" t="n">
         <v>1126.572097368805</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.01</v>
+        <v>-6.51</v>
       </c>
       <c r="L74" t="n">
-        <v>4.4</v>
+        <v>9.35</v>
       </c>
       <c r="M74" t="n">
         <v>0.39</v>
       </c>
       <c r="N74" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O74" t="n">
         <v>1.29</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>10.48</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H75" t="n">
-        <v>1175</v>
+        <v>1186</v>
       </c>
       <c r="I75" t="n">
         <v>1184.864268601822</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.86</v>
+        <v>-6.85</v>
       </c>
       <c r="L75" t="n">
-        <v>6.36</v>
+        <v>7.37</v>
       </c>
       <c r="M75" t="n">
         <v>4.19</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="H76" t="n">
-        <v>1283.3</v>
+        <v>1276.8</v>
       </c>
       <c r="I76" t="n">
         <v>1281.385298225165</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K76" t="n">
-        <v>8.199999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="L76" t="n">
         <v>4.77</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.85</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H77" t="n">
-        <v>1245.4</v>
+        <v>1276.6</v>
       </c>
       <c r="I77" t="n">
         <v>1276.231547274529</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K77" t="n">
-        <v>2.46</v>
+        <v>0.02</v>
       </c>
       <c r="L77" t="n">
         <v>2.87</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,25 +5801,25 @@
         <v>7.34</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H78" t="n">
-        <v>1275.2</v>
+        <v>1253.1</v>
       </c>
       <c r="I78" t="n">
         <v>1253.511823572251</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.11</v>
+        <v>-1.84</v>
       </c>
       <c r="L78" t="n">
         <v>2.84</v>
       </c>
       <c r="M78" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="N78" t="n">
         <v>2.05</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>6.47</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H79" t="n">
-        <v>1260.1</v>
+        <v>1275.2</v>
       </c>
       <c r="I79" t="n">
         <v>1273.130191109658</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="L79" t="n">
         <v>4.03</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>5.13</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H80" t="n">
-        <v>1242.8</v>
+        <v>1206.9</v>
       </c>
       <c r="I80" t="n">
         <v>1230.905437109403</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.54</v>
+        <v>-5.36</v>
       </c>
       <c r="L80" t="n">
-        <v>3.07</v>
+        <v>5.72</v>
       </c>
       <c r="M80" t="n">
         <v>0.54</v>
       </c>
       <c r="N80" t="n">
-        <v>1.6</v>
+        <v>2.89</v>
       </c>
       <c r="O80" t="n">
         <v>1.2</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>6.42</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H81" t="n">
-        <v>1217.5</v>
+        <v>1235.6</v>
       </c>
       <c r="I81" t="n">
         <v>1232.20972276287</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.88</v>
+        <v>-2.38</v>
       </c>
       <c r="L81" t="n">
-        <v>2.88</v>
+        <v>3.64</v>
       </c>
       <c r="M81" t="n">
         <v>3.27</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>6.8</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="H82" t="n">
-        <v>1254.9</v>
+        <v>1209.6</v>
       </c>
       <c r="I82" t="n">
         <v>1234.045001566407</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K82" t="n">
-        <v>1.56</v>
+        <v>-2.1</v>
       </c>
       <c r="L82" t="n">
         <v>5.54</v>
@@ -5115,7 +6098,7 @@
         <v>2.62</v>
       </c>
       <c r="N82" t="n">
-        <v>3.51</v>
+        <v>3.61</v>
       </c>
       <c r="O82" t="n">
         <v>1.49</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>12.38</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H83" t="n">
-        <v>1217</v>
+        <v>1331</v>
       </c>
       <c r="I83" t="n">
         <v>1305.195495502178</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.61</v>
+        <v>-10.04</v>
       </c>
       <c r="L83" t="n">
-        <v>6.22</v>
+        <v>12.19</v>
       </c>
       <c r="M83" t="n">
         <v>2</v>
       </c>
       <c r="N83" t="n">
-        <v>1.72</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O83" t="n">
         <v>-3.61</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>12.4</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="H84" t="n">
-        <v>1349</v>
+        <v>1269.5</v>
       </c>
       <c r="I84" t="n">
         <v>1291.46438788411</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K84" t="n">
-        <v>1.35</v>
+        <v>-4.62</v>
       </c>
       <c r="L84" t="n">
         <v>8.529999999999999</v>
@@ -5229,7 +6236,7 @@
         <v>2.85</v>
       </c>
       <c r="N84" t="n">
-        <v>2.7</v>
+        <v>5.89</v>
       </c>
       <c r="O84" t="n">
         <v>9.369999999999999</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>11.83</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H85" t="n">
-        <v>1185</v>
+        <v>1198.3</v>
       </c>
       <c r="I85" t="n">
         <v>1193.533903177469</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K85" t="n">
-        <v>6.66</v>
+        <v>5.61</v>
       </c>
       <c r="L85" t="n">
         <v>6.26</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5346,6 +6377,14 @@
       <c r="Q86" t="n">
         <v>26</v>
       </c>
+      <c r="R86" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10304,7 +11343,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.4</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="6">
@@ -10314,7 +11353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -10324,7 +11363,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -10334,7 +11373,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -10344,7 +11383,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10354,7 +11393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -10364,7 +11403,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -10374,7 +11413,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -10384,7 +11423,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.5</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="14">
@@ -10394,7 +11433,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.19</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="15">
@@ -10404,7 +11443,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.62</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -10414,7 +11453,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.76</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="17">
@@ -10424,7 +11463,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.17</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="18">
@@ -10434,7 +11473,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -10444,7 +11483,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.71</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="20">
@@ -10454,7 +11493,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.27</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="21">
@@ -10464,7 +11503,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.21</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="22">
@@ -10474,7 +11513,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -10484,7 +11523,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -10494,7 +11533,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="25">
@@ -10514,7 +11553,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.06</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
@@ -10524,7 +11563,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.41</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="28">
@@ -10534,7 +11573,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
